--- a/data/trans_bre/IP1001-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Edad-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 3,23</t>
+          <t>-3,9; 2,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,24</t>
+          <t>-1,11; 3,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,91</t>
+          <t>-2,36; 0,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 0,0</t>
+          <t>-5,79; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 371,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,07</t>
+          <t>-1,79; 1,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,26</t>
+          <t>-3,22; 1,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,1</t>
+          <t>-2,19; 1,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,4</t>
+          <t>-2,54; 2,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,61; 233,68</t>
+          <t>-100,0; 212,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,14; 97,75</t>
+          <t>-79,16; 112,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,88; 176,89</t>
+          <t>-73,86; 167,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,95; 406,47</t>
+          <t>-79,62; 385,47</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 3,8</t>
+          <t>-3,63; 3,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,55</t>
+          <t>-4,14; 1,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 4,71</t>
+          <t>-1,68; 4,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 1,57</t>
+          <t>-7,36; 1,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,8; 175,0</t>
+          <t>-61,89; 177,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-45,39; 230,23</t>
+          <t>-39,6; 260,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-90,64; 94,94</t>
+          <t>-87,36; 101,41</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 5,44</t>
+          <t>-1,17; 5,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 1,43</t>
+          <t>-4,83; 1,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 0,2</t>
+          <t>-5,7; -0,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 0,4</t>
+          <t>-5,24; 0,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,26; 284,07</t>
+          <t>-30,76; 283,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,71; 69,27</t>
+          <t>-79,28; 75,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-94,65; 60,01</t>
+          <t>-100,0; 58,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,65; 32,27</t>
+          <t>-82,95; 13,58</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,71</t>
+          <t>-1,02; 1,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,57</t>
+          <t>-2,1; 0,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,03</t>
+          <t>-1,68; 0,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 0,15</t>
+          <t>-3,25; 0,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,0; 81,16</t>
+          <t>-30,4; 91,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-61,45; 30,22</t>
+          <t>-62,11; 28,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-50,94; 51,19</t>
+          <t>-50,03; 50,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-66,49; 12,66</t>
+          <t>-68,88; 15,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1001-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Edad-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 2,97</t>
+          <t>-3,8; 2,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,09</t>
+          <t>-1,01; 3,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,91</t>
+          <t>-2,37; 0,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 0,0</t>
+          <t>-6,0; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 371,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,07</t>
+          <t>-1,88; 1,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,39</t>
+          <t>-3,28; 1,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,9</t>
+          <t>-2,26; 1,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 2,53</t>
+          <t>-2,59; 2,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 212,23</t>
+          <t>-86,67; 296,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,16; 112,35</t>
+          <t>-84,97; 86,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-73,86; 167,86</t>
+          <t>-72,65; 164,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-79,62; 385,47</t>
+          <t>-82,25; 411,42</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 3,81</t>
+          <t>-3,73; 3,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 1,44</t>
+          <t>-3,96; 1,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 4,88</t>
+          <t>-2,04; 4,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 1,79</t>
+          <t>-7,44; 1,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-61,89; 177,71</t>
+          <t>-62,27; 161,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 264,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-39,6; 260,05</t>
+          <t>-47,51; 252,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-87,36; 101,41</t>
+          <t>-89,11; 92,48</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 5,24</t>
+          <t>-0,96; 5,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 1,49</t>
+          <t>-4,79; 1,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,7; -0,06</t>
+          <t>-5,25; 0,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 0,31</t>
+          <t>-5,0; 0,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,76; 283,87</t>
+          <t>-28,44; 281,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,28; 75,3</t>
+          <t>-81,85; 72,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 58,44</t>
+          <t>-94,0; 45,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,95; 13,58</t>
+          <t>-81,52; 40,23</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,82</t>
+          <t>-1,05; 1,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,48</t>
+          <t>-2,0; 0,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,93</t>
+          <t>-1,66; 1,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,28</t>
+          <t>-3,23; 0,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 91,15</t>
+          <t>-33,83; 88,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-62,11; 28,04</t>
+          <t>-59,97; 39,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-50,03; 50,12</t>
+          <t>-50,5; 63,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-68,88; 15,22</t>
+          <t>-69,98; 8,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1001-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>-1,27</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 2,94</t>
+          <t>-3,51; 3,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 3,21</t>
+          <t>-0,95; 3,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,93</t>
+          <t>-2,42; 0,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 0,0</t>
+          <t>-7,41; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-1,77%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 1,07</t>
+          <t>-1,96; 1,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 1,27</t>
+          <t>-3,25; 1,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,93</t>
+          <t>-2,27; 2,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 2,54</t>
+          <t>-2,58; 2,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-86,67; 296,76</t>
+          <t>-88,61; 233,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-84,97; 86,43</t>
+          <t>-82,14; 97,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,65; 164,25</t>
+          <t>-71,88; 176,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-82,25; 411,42</t>
+          <t>-78,49; 468,56</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,69</t>
+          <t>-0,5</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-38,05%</t>
+          <t>-14,95%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 3,85</t>
+          <t>-3,84; 3,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,44</t>
+          <t>-4,03; 1,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 4,5</t>
+          <t>-1,88; 4,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 1,61</t>
+          <t>-3,79; 2,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,27; 161,99</t>
+          <t>-63,8; 175,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 264,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-47,51; 252,89</t>
+          <t>-45,39; 230,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-89,11; 92,48</t>
+          <t>-76,14; 175,76</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,12</t>
+          <t>-1,88</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-48,45%</t>
+          <t>-42,54%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 5,77</t>
+          <t>-1,14; 5,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 1,58</t>
+          <t>-4,84; 1,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 0,28</t>
+          <t>-5,43; 0,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 0,51</t>
+          <t>-5,07; 0,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 281,84</t>
+          <t>-28,26; 284,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,85; 72,34</t>
+          <t>-81,71; 69,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-94,0; 45,67</t>
+          <t>-94,65; 60,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,52; 40,23</t>
+          <t>-78,45; 51,15</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-40,57%</t>
+          <t>-31,01%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,84</t>
+          <t>-1,11; 1,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,64</t>
+          <t>-2,11; 0,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,09</t>
+          <t>-1,66; 1,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,16</t>
+          <t>-2,63; 0,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,83; 88,36</t>
+          <t>-33,0; 81,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-59,97; 39,68</t>
+          <t>-61,45; 30,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-50,5; 63,33</t>
+          <t>-50,94; 51,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-69,98; 8,57</t>
+          <t>-60,77; 28,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1001-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,183 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,27</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-16,6%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>96,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-51,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.4020120823843346</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.8694942914079441</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.494298375981604</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.273461871527139</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.1659570119557547</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.9681227461770732</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.5186719358840626</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,51; 3,23</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-0,95; 3,24</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,42; 0,91</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-7,41; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.506143551349128</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-0.9515211334338611</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.418055706388488</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-7.410381221926335</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.23156413137248</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.236371652401294</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9147354807212796</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,92</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-21,9%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-33,66%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-6,85%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,96; 1,07</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,25; 1,26</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,27; 2,1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,58; 2,78</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-88,61; 233,68</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-82,14; 97,75</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-71,88; 176,89</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-78,49; 468,56</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.2864994213907943</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.9167175582348124</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.1501815022936632</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.03223131672258489</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2189960515350994</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.336584738320067</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.06846203065348921</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.01528395706110724</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,99</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-40,38%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,19%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-14,95%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.964802177788363</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.251541225830504</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.272605086073278</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.584868748072746</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.8861275267195677</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.8213874902086705</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.7188319531261372</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.7849156611354858</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3,84; 3,8</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,03; 1,55</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,88; 4,71</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-3,79; 2,68</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-63,8; 175,0</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-45,39; 230,23</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-76,14; 175,76</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.072159962314834</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.256474750524136</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.095160360752281</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.784222236090697</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>2.336809734043943</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.9774644358748629</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.768880101908022</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>4.685571094206432</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +803,293 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,69</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-2,29</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,88</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>58,25%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-39,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-65,53%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-42,54%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.009113154385971545</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.9915745235201709</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.283282419015157</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.5006724387651134</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.002103823266772067</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.4038130710857182</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.3819447977061313</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.1495313808237828</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,14; 5,44</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,84; 1,43</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-5,43; 0,2</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-5,07; 0,88</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-28,26; 284,07</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-81,71; 69,27</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-94,65; 60,01</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-78,45; 51,15</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.836978061200207</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.033903372089135</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.877151290413687</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-3.786054315241706</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.637970146445447</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="n">
+        <v>-0.4538750601085266</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.7614251747525304</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.795863270305522</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.548651634157946</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.711174571863774</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.676442826090987</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.749983523558929</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="n">
+        <v>2.302322340130156</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.757554994848512</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.946896538535418</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.686960050358653</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-2.286427206954362</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.876245544444951</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.582518949585949</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3986895293360892</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.6552855577620254</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.4253724188412277</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.139633443102955</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.83949964426003</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-5.425367797474357</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-5.067815596863523</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2826245639110787</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.8171252999621241</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.9464916205463941</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.7845273668225489</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.438287465703805</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.434884097945833</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1968100835083254</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.8784672510890715</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2.840729974493919</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.692735680870228</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.600093490201402</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.5114633405941377</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,77</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,05%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-28,83%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-13,43%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-31,01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,11; 1,71</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,11; 0,57</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,66; 1,03</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,63; 0,61</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-33,0; 81,16</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-61,45; 30,22</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-50,94; 51,19</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-60,77; 28,34</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.3479837377207973</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.7704541181367721</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.3472149470705965</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.043250879254245</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1304626181289897</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.2882546277689301</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.1343284913305255</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.3101436614741644</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.112944902190396</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.105540800601796</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.659850253478587</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.63284861169541</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3299777658609955</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.6144771801611679</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.5094030581038214</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.6076596862543228</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.706172614419963</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.5724335433685906</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.030436157666736</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.6145102464953157</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.8115986182338182</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.3022012739288876</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.5118708275832577</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.2834139267962326</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1097,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
